--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="123">
   <si>
     <t>48949</t>
   </si>
@@ -115,40 +115,109 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>19AAEA4F70049E4EC6F3F4C31D8CEA42</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>1B246A0AADB27B66F48BB669F3BBEFB8</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>58DBD212EA477AD34335947483425E68</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
+  </si>
+  <si>
+    <t>CA1C819C61D512D8100BDF8B89662B41</t>
+  </si>
+  <si>
+    <t>Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
+  </si>
+  <si>
+    <t>EDEF2279BA79E116AF2D048CE3AE3DFB</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
+  </si>
+  <si>
+    <t>44F4880630B72AB13740328EB7E6BE4D</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
+  </si>
+  <si>
+    <t>EB08771B42529500E3AF05D8ACD2E6FB</t>
+  </si>
+  <si>
+    <t>Jefes de Materia</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
+  </si>
+  <si>
+    <t>829CE7B1FF67AB35CE888F41F74550AF</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
+  </si>
+  <si>
+    <t>3763CC85EFBE6801E3124FE421182621</t>
+  </si>
+  <si>
+    <t>Departamento de Planeación e Infraestructura Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
+  </si>
+  <si>
+    <t>BD6F8810D0E109B8C0DE48E62DBB8B62</t>
   </si>
   <si>
     <t>Departamento de Información y Relaciones Públicas</t>
   </si>
   <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2019%20Dpto.%20de%20Informacion%20y%20rel%20publicas.docx</t>
   </si>
   <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
-  </si>
-  <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>5D50FC051554CA1C7631B05CF1CBA1FE</t>
+    <t>EC026493F79FC1F5795475FB7E172948</t>
   </si>
   <si>
     <t>Dirección Académica</t>
@@ -157,7 +226,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
   </si>
   <si>
-    <t>B41F83529AD6CDA90CBB2BD74FA272A0</t>
+    <t>D10A8A404A9B4206EFEAA0E353190E1D</t>
   </si>
   <si>
     <t>Subdirección de Seguimiento Académico</t>
@@ -166,43 +235,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
   </si>
   <si>
-    <t>ECE180C7798C31255B1DEC3D2116629B</t>
-  </si>
-  <si>
-    <t>Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
-  </si>
-  <si>
-    <t>558A5BF2240EDC12E558F7D8364BC132</t>
-  </si>
-  <si>
-    <t>Departamento de  Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
-  </si>
-  <si>
-    <t>174593E600DB1AE3AF9F959C45603DF4</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
-  </si>
-  <si>
-    <t>9E452B9F89460086D8A36C65747E2E28</t>
-  </si>
-  <si>
-    <t>Jefes de Materia</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
-  </si>
-  <si>
-    <t>23EE6D35DF42FB884AF431D428453D6E</t>
+    <t>7182789F9168DBC81002B426B6EEFA78</t>
   </si>
   <si>
     <t>Subdirección de Servicios Escolares</t>
@@ -211,7 +244,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
   </si>
   <si>
-    <t>1D7CC0B7283F0B2950DA95FC1691F074</t>
+    <t>076B6570BB272A0B2D566ECE102D0A8D</t>
   </si>
   <si>
     <t>Departamento de Control Escolar</t>
@@ -220,7 +253,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
   </si>
   <si>
-    <t>10F6F6CB9F623B8EA8CAD4A1D7E1E166</t>
+    <t>CB2E0DBB1639B530A80ECE2CE7AC123D</t>
   </si>
   <si>
     <t>Departamento de Orientación Educativa y Servicio Social</t>
@@ -229,7 +262,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
   </si>
   <si>
-    <t>42793BAF41FF56B0F4DD6DE1956D14C4</t>
+    <t>EB34B4E48C61624B37D5D49882E42469</t>
   </si>
   <si>
     <t>Subdirección de Actividades Paraescolares</t>
@@ -238,7 +271,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
   </si>
   <si>
-    <t>CBE1C0B3BF31D39E7925A4F1CE215F19</t>
+    <t>8815B40337BAE1CF019593B08C9F556E</t>
   </si>
   <si>
     <t>Departamento de Actividades Deportivas y Culturales</t>
@@ -247,25 +280,40 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
   </si>
   <si>
-    <t>EEAEDFDB4ED4C15188A05D8B23F6C939</t>
+    <t>066A31A0C54D7111C4FB83201D881EF0</t>
   </si>
   <si>
     <t>Dirección Administrativa</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2031%20Direcci%C3%B3n%20Admnistrativa.docx</t>
-  </si>
-  <si>
-    <t>B4991CCA318E03A11663FED257F40688</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
   </si>
   <si>
-    <t>F9AA17C26C89B6B0B5BDE97861FED0E5</t>
+    <t>4286C4B37DAB4E6E959C61A0AACC3844</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Adminsitrativos</t>
+  </si>
+  <si>
+    <t>79794E495B296CBF86C11BF00CDD5490</t>
+  </si>
+  <si>
+    <t>Departamento Inventarios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
+  </si>
+  <si>
+    <t>471B8201B0A23047187D692EC129390A</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
+  </si>
+  <si>
+    <t>76844C0613D5A39E0DC14D6C8843AF3A</t>
   </si>
   <si>
     <t>Departamento de Recursos Humanos</t>
@@ -274,34 +322,25 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
   </si>
   <si>
-    <t>1516172BA865F04AFDE8E39AFB546A97</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
+    <t>F29A72263E824173B98FA2A7F1271287</t>
+  </si>
+  <si>
+    <t>Departamento de Recuros Materiales y  Servicios Generales</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
   </si>
   <si>
-    <t>5A77A9AF95B2D42DE536ABFEC26E900C</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
-  </si>
-  <si>
-    <t>46F258ED1192348AF40C254BC88E8522</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
-  </si>
-  <si>
-    <t>93C36256A9591E34E7124248445BA61B</t>
+    <t>7A1FAF3241DE8B0AEC65E4CB5FE2DEC5</t>
+  </si>
+  <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
+  </si>
+  <si>
+    <t>A86E3AEF3146341E02C0CCD898AF4AEF</t>
   </si>
   <si>
     <t>Departamento de Contabilidad</t>
@@ -310,16 +349,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
   </si>
   <si>
-    <t>629F342E7D01FE1F62DE6459336E319D</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
-  </si>
-  <si>
-    <t>F79BBC938B40ECD0198F400AA6E8E5DD</t>
+    <t>414BF622859F033970219D791C105DC0</t>
   </si>
   <si>
     <t>Coordinaciones Sectoriales</t>
@@ -328,7 +358,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
   </si>
   <si>
-    <t>F67AD6A74EDAC9CEF6E081575BAF0E48</t>
+    <t>4BD546D2C89EAAFBA541C0BEF669EDD7</t>
   </si>
   <si>
     <t>Direcciones de cada Plantel</t>
@@ -337,7 +367,7 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
   </si>
   <si>
-    <t>885BD6AABB50502B640B82F34563313F</t>
+    <t>A9E8D9D7F582B0E66D3BCB7BAE2CF7FE</t>
   </si>
   <si>
     <t>Unidad de Control Interno</t>
@@ -346,46 +376,13 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
   </si>
   <si>
-    <t>110128AD6B3D1E95DCD30756873224AD</t>
+    <t>08AB5385E0BAC0335977E8CF0723AC50</t>
   </si>
   <si>
     <t>Dirección General</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
-  </si>
-  <si>
-    <t>3DB3243A5C4A4C75EB4CA4FCB45BF5CB</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
-  </si>
-  <si>
-    <t>8A3E2AEBD9AE1DC8D17CA13A7DA46021</t>
-  </si>
-  <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
-  </si>
-  <si>
-    <t>EC8866AB21FB93D3FCC6BE818378B359</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
-  </si>
-  <si>
-    <t>F25232035CC9FBBF8DD972FF85B30232</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación e Infraestrucura Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
   </si>
 </sst>
 </file>
@@ -781,11 +778,11 @@
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="111.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="188" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
@@ -991,13 +988,13 @@
         <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>40</v>
@@ -1014,25 +1011,25 @@
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>40</v>
@@ -1049,25 +1046,25 @@
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>40</v>
@@ -1084,25 +1081,25 @@
     </row>
     <row r="12" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>40</v>
@@ -1119,25 +1116,25 @@
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>40</v>
@@ -1154,25 +1151,25 @@
     </row>
     <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>40</v>
@@ -1189,25 +1186,25 @@
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>40</v>
@@ -1224,25 +1221,25 @@
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>40</v>
@@ -1259,25 +1256,25 @@
     </row>
     <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>40</v>
@@ -1294,25 +1291,25 @@
     </row>
     <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>40</v>
@@ -1329,25 +1326,25 @@
     </row>
     <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>40</v>
@@ -1364,25 +1361,25 @@
     </row>
     <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>40</v>
@@ -1399,25 +1396,25 @@
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>40</v>
@@ -1434,25 +1431,25 @@
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>40</v>
@@ -1469,25 +1466,25 @@
     </row>
     <row r="23" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>40</v>
@@ -1504,25 +1501,25 @@
     </row>
     <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>40</v>
@@ -1539,25 +1536,25 @@
     </row>
     <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>40</v>
@@ -1574,25 +1571,25 @@
     </row>
     <row r="26" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>40</v>
@@ -1609,25 +1606,25 @@
     </row>
     <row r="27" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>40</v>
@@ -1644,25 +1641,25 @@
     </row>
     <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>40</v>
@@ -1679,25 +1676,25 @@
     </row>
     <row r="29" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>40</v>
@@ -1714,25 +1711,25 @@
     </row>
     <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>40</v>
@@ -1749,25 +1746,25 @@
     </row>
     <row r="31" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>40</v>
@@ -1784,25 +1781,25 @@
     </row>
     <row r="32" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>40</v>
@@ -1819,25 +1816,25 @@
     </row>
     <row r="33" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>40</v>
@@ -1854,25 +1851,25 @@
     </row>
     <row r="34" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>40</v>
@@ -1889,25 +1886,25 @@
     </row>
     <row r="35" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>40</v>
